--- a/lesson16-phuchuy/Java24 PhucHuy Database Design.xlsx
+++ b/lesson16-phuchuy/Java24 PhucHuy Database Design.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huyla\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lap Trinh\JAVA 24\3. DATABASE\lesson16-phuchuy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8C5911-260E-478D-9D0F-AEF7B129440F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEC28CC-C0DB-40FA-8BF1-5423382DA77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1988,7 +1988,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2093,6 +2093,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5941,10 +5944,10 @@
       <c r="I222" s="5"/>
     </row>
     <row r="223" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B223" s="5" t="s">
+      <c r="B223" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C223" s="5" t="s">
+      <c r="C223" s="26" t="s">
         <v>8</v>
       </c>
       <c r="D223" s="5" t="s">
@@ -5959,10 +5962,10 @@
       <c r="I223" s="5"/>
     </row>
     <row r="224" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B224" s="5" t="s">
+      <c r="B224" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C224" s="5" t="s">
+      <c r="C224" s="26" t="s">
         <v>43</v>
       </c>
       <c r="D224" s="5" t="s">
@@ -5977,10 +5980,10 @@
       <c r="I224" s="5"/>
     </row>
     <row r="225" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B225" s="5" t="s">
+      <c r="B225" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="C225" s="5" t="s">
+      <c r="C225" s="26" t="s">
         <v>84</v>
       </c>
       <c r="D225" s="5" t="s">
@@ -5995,10 +5998,10 @@
       <c r="I225" s="5"/>
     </row>
     <row r="226" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B226" s="5" t="s">
+      <c r="B226" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="C226" s="5" t="s">
+      <c r="C226" s="26" t="s">
         <v>171</v>
       </c>
       <c r="D226" s="5" t="s">
@@ -6013,10 +6016,10 @@
       <c r="I226" s="5"/>
     </row>
     <row r="227" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B227" s="5" t="s">
+      <c r="B227" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C227" s="5" t="s">
+      <c r="C227" s="26" t="s">
         <v>0</v>
       </c>
       <c r="D227" s="5" t="s">
@@ -6031,10 +6034,10 @@
       <c r="I227" s="5"/>
     </row>
     <row r="228" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B228" s="5" t="s">
+      <c r="B228" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="C228" s="5" t="s">
+      <c r="C228" s="26" t="s">
         <v>64</v>
       </c>
       <c r="D228" s="5" t="s">
@@ -6049,10 +6052,10 @@
       <c r="I228" s="5"/>
     </row>
     <row r="229" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B229" s="5" t="s">
+      <c r="B229" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="C229" s="5" t="s">
+      <c r="C229" s="26" t="s">
         <v>77</v>
       </c>
       <c r="D229" s="5" t="s">
@@ -6067,10 +6070,10 @@
       <c r="I229" s="5"/>
     </row>
     <row r="230" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B230" s="5" t="s">
+      <c r="B230" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C230" s="5" t="s">
+      <c r="C230" s="26" t="s">
         <v>56</v>
       </c>
       <c r="D230" s="5" t="s">
@@ -6085,10 +6088,10 @@
       <c r="I230" s="5"/>
     </row>
     <row r="231" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B231" s="5" t="s">
+      <c r="B231" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="C231" s="5" t="s">
+      <c r="C231" s="26" t="s">
         <v>68</v>
       </c>
       <c r="D231" s="5" t="s">
@@ -6103,10 +6106,10 @@
       <c r="I231" s="5"/>
     </row>
     <row r="232" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B232" s="5" t="s">
+      <c r="B232" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="C232" s="5" t="s">
+      <c r="C232" s="26" t="s">
         <v>182</v>
       </c>
       <c r="D232" s="5" t="s">
@@ -6121,10 +6124,10 @@
       <c r="I232" s="5"/>
     </row>
     <row r="233" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B233" s="5" t="s">
+      <c r="B233" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C233" s="5" t="s">
+      <c r="C233" s="26" t="s">
         <v>8</v>
       </c>
       <c r="D233" s="5" t="s">
@@ -6139,10 +6142,10 @@
       <c r="I233" s="5"/>
     </row>
     <row r="234" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B234" s="5" t="s">
+      <c r="B234" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C234" s="5" t="s">
+      <c r="C234" s="26" t="s">
         <v>61</v>
       </c>
       <c r="D234" s="35" t="s">
@@ -6157,10 +6160,10 @@
       <c r="I234" s="5"/>
     </row>
     <row r="235" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B235" s="5" t="s">
+      <c r="B235" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C235" s="5" t="s">
+      <c r="C235" s="26" t="s">
         <v>49</v>
       </c>
       <c r="D235" s="17" t="s">
@@ -6175,10 +6178,10 @@
       <c r="I235" s="5"/>
     </row>
     <row r="236" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B236" s="5" t="s">
+      <c r="B236" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="C236" s="5" t="s">
+      <c r="C236" s="26" t="s">
         <v>8</v>
       </c>
       <c r="D236" s="5" t="s">
@@ -6193,10 +6196,10 @@
       <c r="I236" s="5"/>
     </row>
     <row r="237" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B237" s="5" t="s">
+      <c r="B237" s="36" t="s">
         <v>189</v>
       </c>
-      <c r="C237" s="5" t="s">
+      <c r="C237" s="26" t="s">
         <v>15</v>
       </c>
       <c r="D237" s="5" t="s">
